--- a/deliverables/bilal_ganj_master_market_pack_v17_20260416_032251/j40_parts_list_clean_v4_20260416.xlsx
+++ b/deliverables/bilal_ganj_master_market_pack_v17_20260416_032251/j40_parts_list_clean_v4_20260416.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X53"/>
+  <dimension ref="A1:X52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3820,17 +3820,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fuse box - Compact covered ATO/ATC fuse block 6-way</t>
+          <t>EPS kit - Complete EPS column kit with ECU, shafts, U-joints, couplers, brackets, connectors</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>3 identical</t>
+          <t>1 complete kit</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor fuse boxes or new compact covered aftermarket</t>
+          <t>Toyota donor EPS column set (Bilal Ganj: Prius/Corolla/Vitz candidates)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>PKR 11100-21000</t>
+          <t>PKR 54000-136000</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_065030.jpg</t>
+          <t>images/20260321_235600.jpg</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3855,22 +3855,22 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Covered body, firm lid, strong terminals</t>
+          <t>Bench-test smooth assist; no lash/noise; pigtails &gt;=150mm</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg;20260411_143135.jpg</t>
+          <t>20260321_235600.jpg;20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>229</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Reuse original Toyota-style boxes only if terminals are tight and no heat damage.</t>
+          <t>N/A upgrade choice. Existing steering can stay if skipping EPS; EPS is optional improvement.</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3890,27 +3890,27 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Prefer compact new covered fuse boxes online; keep original-style form factor.</t>
+          <t>Bilal Ganj only. Buy complete and bench-tested EPS set; no incomplete kits.</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://wellshop.pk/product/6-way-fuse-block-blade-fuse-box-holder-dc-12-32v-1-709607/</t>
+          <t>Bilal Ganj inspection only</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>BILAL_GANJ_ONLY</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>https://wellshop.pk/product/6-way-fuse-block-blade-fuse-box-holder-dc-12-32v-1-709607/</t>
+          <t>Bilal Ganj (in-person complete kit verification)</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>https://sehgalmotors.pk/products/fuse-60a-box-fuse-kit-for-trucks-and-cars</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EPS kit - Complete EPS column kit with ECU, shafts, U-joints, couplers, brackets, connectors</t>
+          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1 complete kit</t>
+          <t>Full set</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor EPS column set (Bilal Ganj: Prius/Corolla/Vitz candidates)</t>
+          <t>New parts market only (no used donor plugs)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3946,37 +3946,37 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>PKR 54000-136000</t>
+          <t>PKR 12000-36000</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>images/20260321_235600.jpg</t>
+          <t>images/20260317_235150.jpg</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>BUY_IF_ENGINE_CODE_MATCH</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Bench-test smooth assist; no lash/noise; pigtails &gt;=150mm</t>
+          <t>New only; no used/refurbished plugs</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20260321_235600.jpg;20260406_031010.jpg</t>
+          <t>20260317_235150.jpg</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>N/A upgrade choice. Existing steering can stay if skipping EPS; EPS is optional improvement.</t>
+          <t>No. Glow/heat plugs should be new only.</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -3996,27 +3996,27 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bilal Ganj only. Buy complete and bench-tested EPS set; no incomplete kits.</t>
+          <t>Buy new only (engine code/thread/reach confirmed first).</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Bilal Ganj inspection only</t>
+          <t>https://cruisercorps.com/products/ngk-3b-diesel-glow-plug-set-of-4</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>BILAL_GANJ_ONLY</t>
+          <t>BUY_AFTER_ENGINE_CODE</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Bilal Ganj (in-person complete kit verification)</t>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/q_glow%20plug/</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.daraz.pk/catalog/?q=toyota+glow+plug</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4032,17 +4032,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
+          <t>Local front leaf spring pack (new, custom to measured dimensions)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Full set</t>
+          <t>2 packs</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>New parts market only (no used donor plugs)</t>
+          <t>Pakistan local spring manufacturer (Landhi preferred, Popular backup)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4052,47 +4052,47 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>PKR 12000-36000</t>
+          <t>PKR 35000-90000</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>images/20260317_235150.jpg</t>
+          <t>images/20260324_004852.jpg</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>BUY_IF_ENGINE_CODE_MATCH</t>
+          <t>MEASURE_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>New only; no used/refurbished plugs</t>
+          <t>Buy only after measured fit confirmation</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20260317_235150.jpg</t>
+          <t>20260324_004852.jpg;20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>No. Glow/heat plugs should be new only.</t>
+          <t>Maybe. Keep existing only if no cracks, no sag, and bush eyes are within tolerance after mechanic inspection.</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>AS_LISTED</t>
+          <t>MEASURE_FIRST_THEN_BUY</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Unchanged from active parts list.</t>
+          <t>Active local front leaf spring path.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4102,27 +4102,27 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Buy new only (engine code/thread/reach confirmed first).</t>
+          <t>Order custom measured leaf pack from LEW first; use Popular as backup if lead time/price better.</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://cruisercorps.com/products/ngk-3b-diesel-glow-plug-set-of-4</t>
+          <t>https://spring.com.pk/ ; https://popularspringind.com/</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>BUY_AFTER_ENGINE_CODE</t>
+          <t>ACTIVE_SUSPENSION_CORE_ORDER_BY_QUOTE</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/q_glow%20plug/</t>
+          <t>https://spring.com.pk/contact-us/</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/catalog/?q=toyota+glow+plug</t>
+          <t>https://popularspringind.com/</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Local front leaf spring pack (new, custom to measured dimensions)</t>
+          <t>Local rear leaf spring pack (new, custom to measured dimensions)</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -4178,17 +4178,17 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220207.jpg</t>
+          <t>20260324_004852.jpg;20260411_220214.jpg</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Keep existing only if no cracks, no sag, and bush eyes are within tolerance after mechanic inspection.</t>
+          <t>Maybe. Keep existing only if no cracks, no inversion risk, and ride height is acceptable after load check.</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Active local front leaf spring path.</t>
+          <t>Active local rear leaf spring path.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4244,17 +4244,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Local rear leaf spring pack (new, custom to measured dimensions)</t>
+          <t>Steering bushings - Steering linkage bush set</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2 packs</t>
+          <t>1 set</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Pakistan local spring manufacturer (Landhi preferred, Popular backup)</t>
+          <t>New hardware/electrical market (not donor car)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4264,47 +4264,47 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>PKR 35000-90000</t>
+          <t>PKR 3000-12000</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>images/20260324_004852.jpg</t>
+          <t>images/20260406_031010.jpg</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>MEASURE_THEN_BUY_ACTIVE</t>
+          <t>INSPECT_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Buy only after measured fit confirmation</t>
+          <t>Condition-based quote</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220214.jpg</t>
+          <t>20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>230</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Keep existing only if no cracks, no inversion risk, and ride height is acceptable after load check.</t>
+          <t>Maybe. Replace only if measurable play, cracking, or steering looseness persists after service.</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>MEASURE_FIRST_THEN_BUY</t>
+          <t>BUY_ONLY_IF_PLAY_FOUND</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Active local rear leaf spring path.</t>
+          <t>Steering bushing only if wear/play confirmed.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4314,29 +4314,25 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Order custom measured leaf pack from LEW first; use Popular as backup if lead time/price better.</t>
+          <t>Use only if play exists. Prefer new bushings from verified supplier; avoid random used pieces.</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>https://spring.com.pk/ ; https://popularspringind.com/</t>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>ACTIVE_SUSPENSION_CORE_ORDER_BY_QUOTE</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>https://spring.com.pk/contact-us/</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>https://popularspringind.com/</t>
-        </is>
-      </c>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
           <t>NOT_PURCHASED</t>
@@ -4350,17 +4346,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Steering bushings - Steering linkage bush set</t>
+          <t>Wire rework - Split overlength heavy feed wire into 3 serviceable segments</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1 set</t>
+          <t>3 segments</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>New hardware/electrical market (not donor car)</t>
+          <t>Electrical workshop service (rework existing wires)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4370,47 +4366,47 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000</t>
+          <t>PKR 3000-12000 (labor + lugs/heat-shrink re-termination)</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>images/20260406_031010.jpg</t>
+          <t>images/20260411_065030.jpg</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>INSPECT_THEN_BUY_ACTIVE</t>
+          <t>WORKSHOP_TASK</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Condition-based quote</t>
+          <t>Cut+terminate+heat-shrink+continuity/voltage-drop test</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20260406_031010.jpg</t>
+          <t>20260411_065030.jpg;20260321_235600.jpg</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>Electrical_Master</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Replace only if measurable play, cracking, or steering looseness persists after service.</t>
+          <t>Yes. Rework existing overlength cable by cutting into 3 segments and re-terminating.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>BUY_ONLY_IF_PLAY_FOUND</t>
+          <t>DONE_VERIFY_INSTALL</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Steering bushing only if wear/play confirmed.</t>
+          <t>Unchanged from active parts list.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4420,59 +4416,67 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Use only if play exists. Prefer new bushings from verified supplier; avoid random used pieces.</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
-        </is>
-      </c>
+          <t>No change.</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
-        </is>
-      </c>
+          <t>DONE_VERIFY_INSTALL</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
       <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>NOT_PURCHASED</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr"/>
-      <c r="V41" s="2" t="inlineStr"/>
-      <c r="W41" s="2" t="inlineStr"/>
-      <c r="X41" s="2" t="inlineStr"/>
+          <t>COMPLETED_ON_HAND</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>Task completed: 25mm² main feed split into 3 segments</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>Included in market work (cost not logged yet)</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>PWR-04/PWR-05/PWR-06 split done as planned. Recheck crimp quality + continuity before final install.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Wire rework - Split overlength heavy feed wire into 3 serviceable segments</t>
+          <t>Electrical tape (automotive PVC, 19mm x 18-20m)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>3 segments</t>
+          <t>10 rolls</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Electrical workshop service (rework existing wires)</t>
+          <t>New electrical market (not donor car)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000 (labor + lugs/heat-shrink re-termination)</t>
+          <t>PKR 1500-4500</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -4482,32 +4486,32 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP_TASK</t>
+          <t>BUY_NOW</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Cut+terminate+heat-shrink+continuity/voltage-drop test</t>
+          <t>Good adhesive and heat tolerance, not brittle PVC</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg;20260321_235600.jpg</t>
+          <t>20260411_065030.jpg</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Electrical_Master</t>
+          <t>SUB-17</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Yes. Rework existing overlength cable by cutting into 3 segments and re-terminating.</t>
+          <t>N/A consumable item; buy new.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>DONE_VERIFY_INSTALL</t>
+          <t>AS_LISTED</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -4522,52 +4526,48 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>No change.</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr"/>
+          <t>Standard consumable; online purchase is fine.</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.daraz.pk/catalog/?q=electrical+tape+19mm</t>
+        </is>
+      </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>DONE_VERIFY_INSTALL</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
+          <t>BUY_NOW</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.daraz.pk/catalog/?q=electrical+tape+19mm</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ubuy.com.pk/en/search/index/view/product/B0B5VQW6XK/s/3m-electrical-tape-19mm/store/store</t>
+        </is>
+      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED_ON_HAND</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>Task completed: 25mm² main feed split into 3 segments</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>Included in market work (cost not logged yet)</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>PWR-04/PWR-05/PWR-06 split done as planned. Recheck crimp quality + continuity before final install.</t>
-        </is>
-      </c>
+          <t>NOT_PURCHASED</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Electrical tape (automotive PVC, 19mm x 18-20m)</t>
+          <t>Cloth harness loom tape (Tesa-style)</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>10 rolls</t>
+          <t>5 rolls</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>PKR 1500-4500</t>
+          <t>PKR 2500-9000</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Good adhesive and heat tolerance, not brittle PVC</t>
+          <t>Automotive-grade cloth tape; abrasion and heat resistance</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>SUB-17</t>
+          <t>SUB-23</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/catalog/?q=electrical+tape+19mm</t>
+          <t>https://www.daraz.pk/products/19mmx15m-universal-heat-resistant-nap-adhesive-cloth-electrical-automotive-tape-i281397325.html</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/catalog/?q=electrical+tape+19mm</t>
+          <t>https://www.daraz.pk/products/19mmx15m-universal-heat-resistant-nap-adhesive-cloth-electrical-automotive-tape-i281397325.html</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>https://www.ubuy.com.pk/en/search/index/view/product/B0B5VQW6XK/s/3m-electrical-tape-19mm/store/store</t>
+          <t>https://www.daraz.pk/catalog/?q=automotive+cloth+harness+tape</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Cloth harness loom tape (Tesa-style)</t>
+          <t>Firewall grommet assortment</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>5 rolls</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4683,17 +4683,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>PKR 2500-9000</t>
+          <t>PKR 2000-7000</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_065030.jpg</t>
+          <t>images/20260411_143135.jpg</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Automotive-grade cloth tape; abrasion and heat resistance</t>
+          <t>Hole ID/OD fit and thickness for firewall panels</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg</t>
+          <t>20260411_143135.jpg</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>SUB-23</t>
+          <t>SUB-11</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/products/19mmx15m-universal-heat-resistant-nap-adhesive-cloth-electrical-automotive-tape-i281397325.html</t>
+          <t>https://www.daraz.pk/catalog/?q=firewall+grommet+assortment</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/products/19mmx15m-universal-heat-resistant-nap-adhesive-cloth-electrical-automotive-tape-i281397325.html</t>
+          <t>https://www.daraz.pk/catalog/?q=firewall+grommet+assortment</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>https://www.daraz.pk/catalog/?q=automotive+cloth+harness+tape</t>
+          <t>https://www.ubuy.com.pk/en/product/F3KO60UI-swpeet-246pcs-sae-metric-grease-nipple-assortment-kit-hydraulic-grease-fittings-standard-with-plasti</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -4774,17 +4774,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Firewall grommet assortment</t>
+          <t>EPS donor candidate - Toyota Prius column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>1 complete kit</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>New electrical market (not donor car)</t>
+          <t>Toyota donor car (Bilal Ganj)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4794,37 +4794,37 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>PKR 2000-7000</t>
+          <t>PKR 60000-150000</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_143135.jpg</t>
+          <t>images/20260321_235600.jpg</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>QUOTE_ONLY</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Hole ID/OD fit and thickness for firewall panels</t>
+          <t>Motor smooth assist, ECU + shafts + U-joints + couplers + brackets + pigtails included</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20260411_143135.jpg</t>
+          <t>20260321_235600.jpg;20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>SUB-11</t>
+          <t>229-C1</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>N/A consumable item; buy new.</t>
+          <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -4844,29 +4844,17 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Standard consumable; online purchase is fine.</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daraz.pk/catalog/?q=firewall+grommet+assortment</t>
-        </is>
-      </c>
+          <t>No change.</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daraz.pk/catalog/?q=firewall+grommet+assortment</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ubuy.com.pk/en/product/F3KO60UI-swpeet-246pcs-sae-metric-grease-nipple-assortment-kit-hydraulic-grease-fittings-standard-with-plasti</t>
-        </is>
-      </c>
+          <t>KEEP_AS_ACTIVE</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
           <t>NOT_PURCHASED</t>
@@ -4880,7 +4868,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Prius column assist set (complete kit)</t>
+          <t>EPS donor candidate - Toyota Corolla/Axio column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4900,7 +4888,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>PKR 60000-150000</t>
+          <t>PKR 55000-140000</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4915,7 +4903,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Motor smooth assist, ECU + shafts + U-joints + couplers + brackets + pigtails included</t>
+          <t>No lash/noise, compatible column length, complete ECU/connectors/shafts</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -4925,7 +4913,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>229-C1</t>
+          <t>229-C2</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -4974,7 +4962,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Corolla/Axio column assist set (complete kit)</t>
+          <t>EPS donor candidate - Toyota Vitz/Yaris column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -4994,7 +4982,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PKR 55000-140000</t>
+          <t>PKR 50000-130000</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5009,7 +4997,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>No lash/noise, compatible column length, complete ECU/connectors/shafts</t>
+          <t>Column mount and spline compatibility; complete wiring pigtails and couplers</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5019,7 +5007,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>229-C2</t>
+          <t>229-C3</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -5068,17 +5056,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Vitz/Yaris column assist set (complete kit)</t>
+          <t>Rear anti-inversion kit - FK08 (spring flip prevention)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1 complete kit</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor car (Bilal Ganj)</t>
+          <t>OME/EMU supplier or suspension fabricator</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -5088,47 +5076,47 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>PKR 50000-130000</t>
+          <t>PKR 12000-35000</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>images/20260321_235600.jpg</t>
+          <t>images/20260411_220214.jpg</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>QUOTE_ONLY</t>
+          <t>CONDITIONAL_LOCAL_ACTIVE</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Column mount and spline compatibility; complete wiring pigtails and couplers</t>
+          <t>Bracket geometry for your rear spring setup and axle travel clearance</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20260321_235600.jpg;20260406_031010.jpg</t>
+          <t>20260411_220214.jpg</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>229-C3</t>
+          <t>SUS-10</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
+          <t>Maybe. If current rear springs show no inversion tendency, can defer this item.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>AS_LISTED</t>
+          <t>BUY_ONLY_IF_INVERSION_RISK</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Unchanged from active parts list.</t>
+          <t>Only needed if spring inversion tendency appears.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5138,16 +5126,24 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>No change.</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr"/>
+          <t>Buy only if rear inversion tendency appears after spring setup.</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
+        </is>
+      </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>KEEP_AS_ACTIVE</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr"/>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
+        </is>
+      </c>
       <c r="S48" s="2" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
@@ -5162,17 +5158,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Rear anti-inversion kit - FK08 (spring flip prevention)</t>
+          <t>Shock absorbers (new genuine, Pakistan high-quality path)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>1 full set (front+rear)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>OME/EMU supplier or suspension fabricator</t>
+          <t>Agriauto genuine shocks (KYB/Gabriel global standards), authorized dealer network</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -5182,47 +5178,47 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PKR 12000-35000</t>
+          <t>PKR 25,000-80,000 (quote by exact model fitment)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_220214.jpg</t>
+          <t>images/20260324_004852.jpg</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>CONDITIONAL_LOCAL_ACTIVE</t>
+          <t>QUOTE_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Bracket geometry for your rear spring setup and axle travel clearance</t>
+          <t>Exact fitment length/mount type, new genuine packaging, invoice/warranty</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20260411_220214.jpg</t>
+          <t>20260324_004852.jpg;20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>SUS-10</t>
+          <t>SUS-11</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Maybe. If current rear springs show no inversion tendency, can defer this item.</t>
+          <t>Maybe. Replace if damping is weak, leaking, or ride control is poor.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>BUY_ONLY_IF_INVERSION_RISK</t>
+          <t>QUOTE_FIRST_THEN_BUY</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Only needed if spring inversion tendency appears.</t>
+          <t>Added to active suspension quality plan.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5232,25 +5228,29 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Buy only if rear inversion tendency appears after spring setup.</t>
+          <t>Best locally verifiable quality path is Agriauto genuine shocks (KYB/Gabriel standards, OEM-linked, 6-month warranty statement).</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
+          <t>https://www.agriauto.com.pk/about-us/ ; https://www.agriauto.com.pk/products-post/genuine/ ; https://www.agriauto.com.pk/products-post/shock-absorbers-and-struts/</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>ACTIVE_SUSPENSION_CORE_ORDER_NEW</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>https://www.pakwheels.com/accessories-spare-parts/search/-/ct_steering-suspension/</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr"/>
+          <t>https://www.agriauto.com.pk/distributors-network/</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.agriauto.com.pk/products-post/shock-absorbers-and-struts/</t>
+        </is>
+      </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
           <t>NOT_PURCHASED</t>
@@ -5264,67 +5264,67 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Shock absorbers (new genuine, Pakistan high-quality path)</t>
+          <t>Split corrugated wire conduit / outer protective hosing</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1 full set (front+rear)</t>
+          <t>As purchased (exact length to confirm)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Agriauto genuine shocks (KYB/Gabriel global standards), authorized dealer network</t>
+          <t>Local electrical market</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>PKR 25,000-80,000 (quote by exact model fitment)</t>
+          <t>PKR 1,000-6,000</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>images/20260324_004852.jpg</t>
+          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-12067298280348876343.png</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>QUOTE_THEN_BUY_ACTIVE</t>
+          <t>BUY_NOW_ACTIVE</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Exact fitment length/mount type, new genuine packaging, invoice/warranty</t>
+          <t>Correct ID for loom branches, heat tolerance, abrasion resistance</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220207.jpg</t>
+          <t>ai-chat-attachment-12067298280348876343.png</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>SUS-11</t>
+          <t>ELEC-LOOM-01</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Replace if damping is weak, leaking, or ride control is poor.</t>
+          <t>N/A new consumable.</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>QUOTE_FIRST_THEN_BUY</t>
+          <t>PROCURED_ON_HAND</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Added to active suspension quality plan.</t>
+          <t>Added from user market purchase update.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5334,48 +5334,52 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Best locally verifiable quality path is Agriauto genuine shocks (KYB/Gabriel standards, OEM-linked, 6-month warranty statement).</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.agriauto.com.pk/about-us/ ; https://www.agriauto.com.pk/products-post/genuine/ ; https://www.agriauto.com.pk/products-post/shock-absorbers-and-struts/</t>
-        </is>
-      </c>
+          <t>Use split conduit on exposed runs; cloth tape for cabin bundles.</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>ACTIVE_SUSPENSION_CORE_ORDER_NEW</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.agriauto.com.pk/distributors-network/</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.agriauto.com.pk/products-post/shock-absorbers-and-struts/</t>
-        </is>
-      </c>
+          <t>PROCURED_ON_HAND</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>NOT_PURCHASED</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr"/>
-      <c r="V50" s="2" t="inlineStr"/>
-      <c r="W50" s="2" t="inlineStr"/>
-      <c r="X50" s="2" t="inlineStr"/>
+          <t>PROCURED_ON_HAND</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>Purchased (length not yet logged)</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>Not logged</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>Bought during market visit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Split corrugated wire conduit / outer protective hosing</t>
+          <t>Booster/charging cable set (MAXXIS Booster Cable 1000 AMP)</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>As purchased (exact length to confirm)</t>
+          <t>1 set</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -5390,12 +5394,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>PKR 1,000-6,000</t>
+          <t>PKR 2,000-10,000</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-12067298280348876343.png</t>
+          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-8920882528865792364.png</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5405,22 +5409,22 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Correct ID for loom branches, heat tolerance, abrasion resistance</t>
+          <t>Clamp quality, copper content, cable gauge, insulation flexibility</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>ai-chat-attachment-12067298280348876343.png</t>
+          <t>ai-chat-attachment-8920882528865792364.png</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>ELEC-LOOM-01</t>
+          <t>ELEC-CHG-01</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>N/A new consumable.</t>
+          <t>Useful workshop support item.</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -5440,7 +5444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Use split conduit on exposed runs; cloth tape for cabin bundles.</t>
+          <t>Use as workshop support; not a substitute for permanent vehicle main feeds.</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr"/>
@@ -5458,7 +5462,7 @@
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>Purchased (length not yet logged)</t>
+          <t>1 set purchased</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
@@ -5480,12 +5484,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Booster/charging cable set (MAXXIS Booster Cable 1000 AMP)</t>
+          <t>Battery terminal clamps / terminators (pair)</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1 set</t>
+          <t>2 terminals</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -5495,17 +5499,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>PKR 2,000-10,000</t>
+          <t>PKR 500-3,000</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-8920882528865792364.png</t>
+          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-4151165269365336421.png</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -5515,27 +5519,27 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Clamp quality, copper content, cable gauge, insulation flexibility</t>
+          <t>Clamp fit on battery posts, material quality, corrosion resistance</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>ai-chat-attachment-8920882528865792364.png</t>
+          <t>ai-chat-attachment-4151165269365336421.png;ai-chat-attachment-14089458610305842598.png</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>ELEC-CHG-01</t>
+          <t>ELEC-BAT-TERM-01</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Useful workshop support item.</t>
+          <t>New terminals are preferred if old ones are worn/oxidized.</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>PROCURED_ON_HAND</t>
+          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -5550,25 +5554,25 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Use as workshop support; not a substitute for permanent vehicle main feeds.</t>
+          <t>Use anti-corrosion paste and correct clamp torque at install.</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>PROCURED_ON_HAND</t>
+          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
       <c r="S52" s="2" t="inlineStr"/>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>PROCURED_ON_HAND</t>
+          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1 set purchased</t>
+          <t>2 terminals purchased</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
@@ -5582,116 +5586,6 @@
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
-        <is>
-          <t>Bought during market visit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Battery terminal clamps / terminators (pair)</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>2 terminals</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Local electrical market</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>PKR 500-3,000</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>/var/folders/2r/rbnydbl91t9_jcjfhssspzqw0000gn/T/ai-chat-attachment-4151165269365336421.png</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>BUY_NOW_ACTIVE</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Clamp fit on battery posts, material quality, corrosion resistance</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>ai-chat-attachment-4151165269365336421.png;ai-chat-attachment-14089458610305842598.png</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>ELEC-BAT-TERM-01</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>New terminals are preferred if old ones are worn/oxidized.</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>Added from user market purchase update.</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>KEPT_IN_ACTIVE</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>Use anti-corrosion paste and correct clamp torque at install.</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr"/>
-      <c r="S53" s="2" t="inlineStr"/>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>PROCURED_ON_HAND_VERIFY_FIT</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>2 terminals purchased</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="W53" s="2" t="inlineStr">
-        <is>
-          <t>Not logged</t>
-        </is>
-      </c>
-      <c r="X53" s="2" t="inlineStr">
         <is>
           <t>Bought during market visit.</t>
         </is>
